--- a/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/ホーム画面/画面処理詳細.xlsx
+++ b/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/ホーム画面/画面処理詳細.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjk037_\Desktop\学習用\家計管理アプリ\b_詳細設計\画面設計\ホーム画面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04356BA-7511-4CE7-9D5E-5C87D9468103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD78B745-1B4A-42AD-9C58-800E5147FD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11970" yWindow="15" windowWidth="15450" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="45" windowWidth="14625" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="118">
   <si>
     <t>表示項目一覧</t>
     <rPh sb="0" eb="2">
@@ -180,16 +181,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>一回の収支について</t>
-    <rPh sb="0" eb="2">
-      <t>イッカイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シュウシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>コンテナ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -342,6 +333,1005 @@
     <t>固定文字列</t>
     <rPh sb="0" eb="5">
       <t>コテイモジレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各収支カード</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>addKakeibo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面が開いたとき</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面を取得した時点の年、月、日を基準にhttp://localhost:8080/index/{year}/{month}/{day}にアクセスすることで</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジテン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下がデータのプロパティ名と、対応する素性である</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>スジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データの通しID</t>
+    <rPh sb="4" eb="5">
+      <t>トオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データが所有する収支カテゴリのid</t>
+    <rPh sb="4" eb="6">
+      <t>ショユウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収支カテゴリ名</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入出金発生日</t>
+    <rPh sb="0" eb="3">
+      <t>ニュウシュッキン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入・収支の種類文字列。「IN」が収入、「OUT」が支出</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハートマークを表示する基準となる、がんばったフラグ。「１」がアクティブ、「０」がネガティブ</t>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収支情報に対する自由メモ入力欄</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記事製作日時（自動生成）</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記事最終更新日時（自動生成）</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトデリートフラグ。削除データは「９」が入力される</t>
+    <rPh sb="11" eb="13">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一か月分総収入</t>
+    <rPh sb="0" eb="1">
+      <t>イッ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲツブン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ソウシュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一か月分総支出</t>
+    <rPh sb="0" eb="1">
+      <t>イッ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲツブン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ソウシシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入-支出</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の給料日（アクセス当日が給料日なら、本日日付を取得）</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キュウリョウビ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウジツ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>キュウリョウビ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一か月分のデータでhomeru＝１なデータの総数</t>
+    <rPh sb="0" eb="1">
+      <t>イッ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲツブン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ソウスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これらのデータをもとに、以下のデータを算出・表示する</t>
+    <rPh sb="12" eb="14">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サンシュツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒字はラベル、赤字は取得データを表示する</t>
+    <rPh sb="0" eb="2">
+      <t>クロジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また収支分類の種別により、カードの背景色を分ける</t>
+    <rPh sb="2" eb="4">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュベツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収支分類：収入のものは#DDEEFF（黄色）、</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収支分類：支出のものは#FFFFEE（青）</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>続いて個別のデータの表示について</t>
+    <rPh sb="0" eb="1">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コベツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以上の内容をカード形式で、日付の新しいものから表示する</t>
+    <rPh sb="0" eb="2">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>カテゴリ名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>金額</t>
+    </r>
+    <rPh sb="4" eb="5">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>入出金発生日　</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💛</t>
+    </r>
+    <rPh sb="0" eb="3">
+      <t>ニュウシュッキン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力日から取得するデータ範囲を調整する機能はバックエンド側が所有しているので、フロント側は給料日を想定したデータ調整は不要</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ショユウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="45" eb="48">
+      <t>キュウリョウビ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ取得範囲を一か月前に移行する。最古のデータよりも古い時期のデータを探そうとしたときは</t>
+    <rPh sb="3" eb="5">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イッ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲツマエ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サイコ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>フル</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Integer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>String</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LocalDate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LocalDateTime</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.id;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.categoryId;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.category;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.tradeDate;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.amount;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.inOut</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.homeru</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.memo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lodata.createdAt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.updatedAt</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.softDelete</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>warning</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最新給料日から本日まで一か月分のデータをjson配列の形で、また後に示す月めくり命令に対してのバックエンド側の回答を文字列で返される</t>
+    <rPh sb="0" eb="2">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キュウリョウビ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イッ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゲツブン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ノチ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="58" eb="61">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月めくり命令の結果文字列</t>
+    <rPh sb="0" eb="1">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>モジレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バックエンド側の処理により探査期間が一か月プラスされる（つまり現在と同じ期間が表示される）。</t>
+    <rPh sb="6" eb="7">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タンサ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>イッ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この時、バックエンドから返されるデータのwarningプロパティに「BEFORE OLDEST」の文字列が入る。</t>
+    <rPh sb="2" eb="3">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これに対応したエラーメッセージを表示すること。</t>
+    <rPh sb="3" eb="5">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ取得範囲を一か月後に移行する。最古のデータよりも古い時期のデータを探そうとしたときは</t>
+    <rPh sb="3" eb="5">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イッ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サイコ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>フル</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当該月に一つもデータがなく、また前後の月間にデータがある場合はwarningプロパティに「EMPTY」</t>
+    <rPh sb="0" eb="2">
+      <t>トウガイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゼンゴ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゲッカン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロパティが入る。この際もこれに対応したエラーメッセージを表示すること。</t>
+    <rPh sb="6" eb="7">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その下に月めくりボタンを配置する</t>
+    <rPh sb="2" eb="3">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>前の月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>押下</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>次の月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>押下</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>個別収支カード押下</t>
+    <rPh sb="0" eb="2">
+      <t>コベツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対応するカードの個別情報ページへ画面遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コベツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取得したデータのidを利用して「http://localhost:8080/index/showdata/{id}」にアクセスし、</t>
+    <rPh sb="0" eb="2">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細データページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>個別収支カード上のハートマークを押下</t>
+    <rPh sb="0" eb="2">
+      <t>コベツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上のハートマークを赤から灰色、灰色から赤に遷移する。</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハイイロ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハイイロ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>該当する収支データのidを利用して「http://localhost:8080/index//homeru/{id}」にアクセスし、</t>
+    <rPh sb="0" eb="2">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース上の当該idのhomeruを1/0で切り替える</t>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウガイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -350,7 +1340,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +1364,43 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -383,7 +1410,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -391,13 +1418,182 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -678,7 +1874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
@@ -726,7 +1922,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -735,7 +1931,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -754,7 +1950,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -763,12 +1959,12 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -794,7 +1990,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -805,109 +2001,710 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
         <v>50</v>
       </c>
-      <c r="C17" t="s">
-        <v>51</v>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A7E508-4498-4FDB-BC5F-F03CEC0FE52B}">
+  <dimension ref="A1:O72"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="4.125" customWidth="1"/>
+    <col min="5" max="5" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="B5" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="30"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="29"/>
+      <c r="G8" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="30"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="29"/>
+      <c r="G9" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="30"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="30"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="30"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="30"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="30"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="30"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="30"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="30"/>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="30"/>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="30"/>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="B27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="B32" s="13"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="14"/>
+      <c r="C33" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="16"/>
+      <c r="G33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="14"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="6"/>
+      <c r="G34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="14"/>
+      <c r="C35" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="6"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="14"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="6"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="14"/>
+      <c r="C37" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="6"/>
+      <c r="G37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="G38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="14"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="15"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="8"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="D50" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="D51" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="D52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="D53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="D54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="D58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="D59" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="D60" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="D61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="D62" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="D65" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="D66" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="D67" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="D70" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="D71" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="D72" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>